--- a/relatorio/relatorio_despesas.xlsx
+++ b/relatorio/relatorio_despesas.xlsx
@@ -10,9 +10,6 @@
   <sheets>
     <sheet name="Despesas" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Despesas!$A:$D</definedName>
-  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -283,7 +280,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -306,6 +303,10 @@
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -524,88 +525,88 @@
     <row r="21" s="1" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0"/>
-      <c r="B23" s="0"/>
-      <c r="C23" s="0"/>
-      <c r="D23" s="0"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0"/>
-      <c r="B24" s="0"/>
-      <c r="C24" s="0"/>
-      <c r="D24" s="0"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0"/>
-      <c r="B25" s="0"/>
-      <c r="C25" s="0"/>
-      <c r="D25" s="0"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0"/>
-      <c r="B26" s="0"/>
-      <c r="C26" s="0"/>
-      <c r="D26" s="0"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0"/>
-      <c r="B27" s="0"/>
-      <c r="C27" s="0"/>
-      <c r="D27" s="0"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0"/>
-      <c r="B28" s="0"/>
-      <c r="C28" s="0"/>
-      <c r="D28" s="0"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0"/>
-      <c r="B29" s="0"/>
-      <c r="C29" s="0"/>
-      <c r="D29" s="0"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0"/>
-      <c r="B30" s="0"/>
-      <c r="C30" s="0"/>
-      <c r="D30" s="0"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0"/>
-      <c r="B31" s="0"/>
-      <c r="C31" s="0"/>
-      <c r="D31" s="0"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0"/>
-      <c r="B32" s="0"/>
-      <c r="C32" s="0"/>
-      <c r="D32" s="0"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0"/>
-      <c r="B33" s="0"/>
-      <c r="C33" s="0"/>
-      <c r="D33" s="0"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0"/>
-      <c r="B34" s="0"/>
-      <c r="C34" s="0"/>
-      <c r="D34" s="0"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0"/>
-      <c r="B35" s="0"/>
-      <c r="C35" s="0"/>
-      <c r="D35" s="0"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0"/>
-      <c r="B36" s="0"/>
-      <c r="C36" s="0"/>
-      <c r="D36" s="0"/>
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="8">
